--- a/review-tasks/1a-autotest-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1a-autotest-review/jury/scoring-sheet.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>…понял, что TK900103 зависит от TK900101, и предложил готовить заблокированную карту в самом тесте. Засчитываем замечание и у TK900103, и у TK900101</t>
+          <t>…понял, что TK900103 зависит от TK900101, и предложил готовить заблокированную карту в самом тесте. Засчитываем замечание и у TK900103, и у TK900101. Отличие от Д103.3: там на той же строке не проверен результат шага 1, а здесь данные берутся из другого теста</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>…заметил непроверенный ожидаемый результат шага 1</t>
+          <t>…заметил непроверенный ожидаемый результат шага 1. Отличие от Д103.2: там тест берёт карту из TK900101, здесь после открытия карты не проверен статус</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>…указал на зашитый адрес. Засчитываем и замечание по симптому: при запуске на другом порту TK900113 падает с ERR_CONNECTION_REFUSED</t>
+          <t>…указал на зашитый адрес. Засчитываем и замечание по симптому: при запуске на другом порту TK900113 падает с ERR_CONNECTION_REFUSED. Отличие от Д113.2: там нет трейса, здесь зашит адрес</t>
         </is>
       </c>
     </row>

--- a/review-tasks/1a-autotest-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1a-autotest-review/jury/scoring-sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/review-tasks/1a-autotest-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1a-autotest-review/jury/scoring-sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/review-tasks/1a-autotest-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1a-autotest-review/jury/scoring-sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>0 или 1</t>
+          <t>Найден (1/0)</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>…указал, что пароль попадает в лог или отчёт, и предложил писать только роль или логин</t>
+          <t>…указал, что пароль попадает в лог или отчёт, или предложил писать в лог только роль или логин</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>…предложил ожидание по условию: появление сообщения или значение в поле</t>
+          <t>…понял, что это фиксированная пауза, или предложил ожидание по условию: появление сообщения или значение в поле</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>…понял, что TK900103 зависит от TK900101, и предложил готовить заблокированную карту в самом тесте. Засчитываем замечание и у TK900103, и у TK900101. Отличие от Д103.3: там на той же строке не проверен результат шага 1, а здесь данные берутся из другого теста</t>
+          <t>…понял, что TK900103 зависит от TK900101, или предложил готовить заблокированную карту в самом тесте. Засчитываем замечание и у TK900103, и у TK900101. Отличие от Д103.3: там после открытия карты не проверен статус, а здесь данные берутся из другого теста</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TK900103Test.java:41</t>
+          <t>TK900103Test.java:42</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1: статус «Заблокирована» после открытия карты не проверяется</t>
+          <t>Шаг 1: статус «Заблокирована» после открытия карты не проверяется — вместо проверки комментарий «карта заведомо заблокирована»</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>TK900103Test.java:44–45</t>
+          <t>TK900103Test.java:45–46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>…указал на пароль в коде и предложил брать учётку старшего менеджера из файла учёток или хранилища секретов. Отличие от Д103.1: там зашит адрес стенда</t>
+          <t>…указал на пароль в коде или предложил брать учётку старшего менеджера из файла учёток или хранилища секретов. Отличие от Д103.1: там зашит адрес стенда</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>TK900103Test.java:46–48</t>
+          <t>TK900103Test.java:47–49</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Selenide.sleep(10000) — пауза, а не ожидание. К тому же лишняя: ниже статус новой карты и так ждут по условию до 3 минут</t>
+          <t>Selenide.sleep(10000) — фиксированная пауза вместо ожидания по условию: тест всегда стоит 10 секунд, а если заявка обработается дольше, пауза не поможет. Ждать надо результата — сообщения о заявке или карт в профиле</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>…понял, что это пауза, и предложил ожидание по условию или просто убрать её</t>
+          <t>…понял, что это фиксированная пауза, или предложил ожидание по условию либо просто убрать её</t>
         </is>
       </c>
     </row>
@@ -1214,17 +1214,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>TK900106Test.java:53</t>
+          <t>TK900106Test.java:54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2: ошибка «Превышен максимальный лимит 500 000 ₽» не проверяется вовсе — негативный тест не проверяет главное</t>
+          <t>Шаг 2: ошибка «Превышен максимальный лимит 500 000 ₽» не проверяется вовсе — негативный тест не проверяет главное. Вместо проверки — запись в отчёт, что ошибка отображается</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>…указал, что текст ошибки не проверяется. Отличие от Д106.4: там речь не об ошибке, а о том, что проверка отсутствия «Лимит изменён» срабатывает слишком рано</t>
+          <t>…указал, что текст ошибки не проверяется. Засчитываем и замечание, что запись в отчёт выдаёт непроверенное за проверенное. Отличие от Д106.4: там речь не об ошибке, а о том, что проверка отсутствия «Лимит изменён» срабатывает слишком рано</t>
         </is>
       </c>
     </row>
@@ -1268,17 +1268,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>TK900106Test.java:58</t>
+          <t>TK900106Test.java:59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>assertEquals с аргументами в порядке «ожидаемое, фактическое», а TestNG ждёт «фактическое, ожидаемое»: при падении «ожидалось» и «получено» в сообщении перепутаны</t>
+          <t>Шаг 3: значение поля читается через getValue() один раз и сравнивается в assertEquals: Selenide не ждёт, пока в поле появится нужное значение. Если поле заполнится чуть позже, тест упадёт, хотя лимит верный. Нужно shouldHave(exactValue(DEFAULT_CASH_LIMIT))</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>…заметил перепутанный порядок аргументов. Если участник написал только, что значение поля читается без ожидания, — не засчитываем: замечание верное, но это не этот дефект</t>
+          <t>…понял, что значение поля читается без ожидания, или предложил проверку Selenide с ожиданием. Отличие от Д106.2: там не проверен шаг 1, до изменения лимита</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>…указал, что прогоны зависят друг от друга через общую карту, и предложил готовить данные на каждый прогон. Отличие от Д109.2: там общая глобальная настройка, здесь общая карта. Сам набор из двух границ — не дефект (ловушка Л4)</t>
+          <t>…указал, что прогоны зависят друг от друга через общую карту, или предложил готовить данные на каждый прогон. Отличие от Д109.2: там общая глобальная настройка, здесь общая карта. Сам набор из двух границ — не дефект (ловушка Л4)</t>
         </is>
       </c>
     </row>
@@ -1825,1350 +1825,1350 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Д116.1</t>
+          <t>Д111.1</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>TK900116</t>
+          <t>TK900111</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:62–65</t>
+          <t>TK900111Test.java:13</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2: номер счёта договора не проверяется, хотя кейс требует, чтобы он начинался с 40817; проверены только состояния договора и счёта</t>
+          <t>В @DisplayName номер чужого кейса TK-900115: в отчёте и в Test IT результат окажется под чужим номером, трейс тоже назван по TK-900115, а у TK-900111 результата не будет</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что не проверен номер счёта (балансовый счёт 40817)</t>
+          <t>…заметил, что номер кейса в названии теста не тот. Засчитываем и замечание по симптому: в build/traces два файла «TK-900115 …» и нет файла TK-900111</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Д116.2</t>
+          <t>Д111.2</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>TK900116</t>
+          <t>TK900111</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:71</t>
+          <t>TK900111Test.java:20–22</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Филиал зашит: вместо филиалов, у которых операционный день совпадает с текущей датой, тест всегда идёт в Московский РФ. Комментарий «клиенты с FATCA только в этом филиале» описывает данные одного стенда, и даже там неверен: такие клиенты есть и в Тверском РФ. Если у филиала закроют день или на другом стенде клиентов там нет, тест не найдёт данных</t>
+          <t>Шаг 1: статус «Активна» после открытия карты не проверяется</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>…указал, что филиал зашит и тест привязан к данным одного стенда, или что пропала проверка операционного дня филиала</t>
+          <t>…заметил непроверенный ожидаемый результат шага 1. Отличие от Д111.5: здесь проверки нет совсем, там она есть, но не может упасть</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Д116.3</t>
+          <t>Д111.3</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>TK900116</t>
+          <t>TK900111</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:86</t>
+          <t>TK900111Test.java:26</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>NOT IN по подзапросу, где бывают пустые C_CLIENT (производство ещё не сопоставлено с клиентом): при хотя бы одном пустом значении NOT IN не возвращает ни одной строки, клиент не находится никогда. Нужно NOT EXISTS с условием ep.C_CLIENT = cp.ID</t>
+          <t>page.waitForTimeout(5000) — фиксированная пауза вместо ожидания по условию. Блокировка в песочнице идёт 2 секунды, остальные 3 секунды тест просто стоит, а на медленном стенде 5 секунд может не хватить</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>…связал NOT IN с пустыми значениями в подзапросе и понял, что запрос вернёт пустой результат. Засчитываем и предложение заменить на NOT EXISTS или отсечь пустые значения. Засчитываем и замечание по симптому: тест падает на строке 101 «Клиент ФЛ не найден», если указана причина — условие про исполнительные производства. Отличие от Д116.4: там запрос находит лишних клиентов, здесь не находит никого</t>
+          <t>…указал на паузу или предложил ждать статуса. Засчитываем и замечание по симптому: TK900111 идёт 7–8 секунд, хотя делает не больше других. Отличие от Д111.4: здесь лишняя пауза, там проверка статуса, которая без этой паузы не работает</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Д116.4</t>
+          <t>Д111.4</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>TK900116</t>
+          <t>TK900111</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:87–92</t>
+          <t>TK900111Test.java:27</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>В условии FATCA OR без скобок: AND связывает сильнее, вторая ветка не привязана к клиенту, и при любой чужой действующей форме с датой окончания EXISTS истинно для всех клиентов. Тест берёт клиента без FATCA, открытие договора падает с ошибкой ЦФТ. Скобки, которые QueryBuilder ставит вокруг условия целиком, не помогают — ошибка внутри подзапроса</t>
+          <t>Статус читается через textContent() и сравнивается в assertEquals: значение берётся в момент вызова, без автоожидания. Проверка проходит только благодаря паузе в строке 26: без паузы тест падает с «expected: &lt;Заблокирована&gt; but was: &lt;Обработка…&gt;». Нужно assertThat(cardPage.status()).hasText("Заблокирована")</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>…указал на OR без скобок и понял, что фильтр по клиенту теряется или что найдутся клиенты без формы FATCA. Засчитываем и замечание по симптому: после исправления Д116.3 тест падает на строке 52 с ошибкой ЦФТ «У клиента нет действующей формы FATCA», если причина — условие на FATCA. Отличие от Д116.3: там не находится никто, здесь находятся лишние клиенты</t>
+          <t>…понял, что эта проверка не ждёт статуса и держится на паузе. Отличие от Д111.3: там лишняя пауза, здесь проверка, которая без этой паузы не работает. Замечание «убрать паузу и проверять статус с ожиданием» засчитываем за оба дефекта, если названы обе строки</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Д116.5</t>
+          <t>Д111.5</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>TK900116</t>
+          <t>TK900111</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:101</t>
+          <t>TK900111Test.java:30–33</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>После цикла проверяется только клиент. Если операциониста не нашлось, тест упадёт с NullPointerException в authorization(user), и непонятно, что не нашлись данные</t>
+          <t>Проверка видимости баннера в if не ждёт и смотрит на состояние в эту секунду: если баннера нет, проверка просто не выполняется, а если он есть, проверка внутри if подтверждает уже известное. Ожидаемый результат «отображается баннер» фактически не проверяется</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>…указал, что пользователь после поиска не проверяется и падение будет непонятным</t>
+          <t>…понял, что проверка баннера не может упасть. Засчитываем и формулировку, что условие не ждёт появления баннера. Отличие от Д111.2: там проверки статуса нет совсем, здесь проверка баннера есть, но не может упасть</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Д117.1</t>
+          <t>Д112.1</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>TK900117</t>
+          <t>TK900112</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>CashDepositToCurrentAccountTest.java:77–79</t>
+          <t>TK900112Test.java:15–17</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Комментарий говорит, что на стендах RF проводка идёт до 10 минут, а проверка ждёт состояние «Выполнена» со стандартным таймаутом 60 секунд: на стендах RF тест будет падать, хотя проводка просто идёт дольше</t>
+          <t>Личный долгоживущий JWT-токен (владелец ivanov_ii) в коде вместо токена из Config. Токен даёт доступ к API под чужой учёткой и попадёт в репозиторий. Протухание токена решается в Config — он и так берёт новый токен заранее</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что ожидание короче, чем нужно по комментарию, или что ожидание проводки слишком короткое для стендов RF</t>
+          <t>…указал на токен в коде</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Д117.2</t>
+          <t>Д112.2</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>TK900117</t>
+          <t>TK900112</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>CashDepositToCurrentAccountTest.java:83</t>
+          <t>TK900112Test.java:24–26</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Остаток проверяется как «больше, чем был»: пройдёт при любом увеличении, а кейс требует ровно +1 500,00 ₽</t>
+          <t>Шаг 1: вкладка «Лимиты» не открывается, значение по умолчанию 200 000 не проверяется</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка не сверяет сумму увеличения. Замечание, что у проверки нет сообщения, засчитываем, только если сказано и то, что сумма не сверяется</t>
+          <t>…заметил, что не проверено значение по умолчанию. Отличие от Д112.4: там не проверено значение после обновления страницы, здесь — до изменения</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Д117.3</t>
+          <t>Д112.3</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>TK900117</t>
+          <t>TK900112</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>CashDepositToCurrentAccountTest.java:101</t>
+          <t>TK900112Test.java:31</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Состояние «Работает» задано ID записи справочника RTEST. ID справочника генерируется на каждом стенде свой, одинаков только код: на INTEST тест не найдёт ни одного договора. Нужно withStatusEqualTo(ComStatusPrd.$WORK)</t>
+          <t>Значение поля после сохранения читается через page.querySelector(...): это ElementHandle в обход локаторов CardPage, без автоожидания и по CSS с именем поля. Значение берётся в момент вызова: если поле перерисуется позже, проверка прочитает старое значение, а если поле не найдётся, тест упадёт с NullPointerException. Нужно assertThat(cardPage.transferLimitInput()).hasValue("150 000")</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>…указал, что ID справочника зависит от стенда, или предложил фильтр по коду состояния. Засчитываем и замечание по симптому: на INTEST тест падает на строке 124 «Договор не найден», если причина — ID состояния. Отличие от Д117.4: там зашит пользователь, здесь — запись справочника</t>
+          <t>…указал, что значение в поле проверяется без ожидания или в обход описания страницы. Отличие от Д112.5: там лишнее ожидание после обновления страницы, здесь чтение значения без ожидания на шаге 2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Д117.4</t>
+          <t>Д112.4</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>TK900117</t>
+          <t>TK900112</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>CashDepositToCurrentAccountTest.java:115</t>
+          <t>TK900112Test.java:33–34</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Кассир зашит логином kassir_mn с одного стенда и одного подразделения, а кейс требует кассира подразделения договора. На другом стенде или при смене сотрудника тест сломается</t>
+          <t>Шаг 3: после обновления страницы вкладка «Лимиты» не открывается и значение 150 000 не проверяется — сохранился ли лимит, тест не знает</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>…указал на зашитый логин пользователя и предложил искать кассира по подразделению договора и роли. Отличие от Д117.3: там зашита запись справочника</t>
+          <t>…заметил, что после обновления страницы ничего не проверено. Отличие от Д112.5: здесь нет проверки, там лишнее ожидание. Отличие от Д112.2: там не проверено значение до изменения</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Д117.5</t>
+          <t>Д112.5</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>TK900117</t>
+          <t>TK900112</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>CashDepositToCurrentAccountTest.java:133–136, CashDepositToCurrentAccountTest.java:60–61</t>
+          <t>TK900112Test.java:35</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>«Последняя» операция берётся без ORDER BY и без фильтра по сумме и дате: FETCH FIRST 1 ROWS ONLY возвращает произвольную строку. У договоров есть история операций, тест берёт старую проведённую операцию</t>
+          <t>waitForLoadState(NETWORKIDLE) — ожидание тишины в сети, документация Playwright не советует его в тестах. Тишина в сети не значит, что на странице нужные данные, а если страница постоянно что-то запрашивает в фоне, тишина не наступит и тест упадёт по таймауту. Нужно не ожидание, а проверка значения в поле: она ждёт сама</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>…указал, что без сортировки порядок строк не определён, или что запрос не отличает созданную операцию от старых. Засчитываем, если названо место запроса или его вызова. Засчитываем и замечание по симптому: тест через 60 секунд падает на строках 63–65 — у операции состояние PERFORMED вместо ADD_CONTROL, если указана причина — берётся не та операция. Отличие от Д117.3: там договор не находится вовсе, здесь находится не та операция</t>
+          <t>…указал, что ожидание тишины в сети ненадёжно или не нужно, раз проверка с автоожиданием ждёт сама. Отличие от Д112.4: там нет проверки после обновления. Отличие от Д112.3: там значение читается без ожидания</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Д118.1</t>
+          <t>Д113.1</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>TK900118</t>
+          <t>TK900113</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ArrestOnCurrentAccountTest.java:58–59</t>
+          <t>TK900113Test.java:16–17, TK900113Test.java:21–26, TK900113Test.java:47–48, TK900113Test.java:59–60, TK900113Test.java:67–68</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Вид «Арест», сумма 5 000,00 ₽ и состояние «Действует» созданной блокировки не проверяются: из ожидаемых результатов проверен только доступный остаток</t>
+          <t>Шаги кейса — три отдельных теста с @Order, общими полями и одной страницей на класс. Шаги зависят друг от друга: шаг 2 или 3 отдельно не запустить, cardPage равен null; если упал шаг 1, шаги 2–3 падают с посторонними ошибками; в отчёте один кейс превращается в три результата. Нужен один тест, шаги — через Allure.step</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>…указал, что не проверены вид, сумма или состояние блокировки. Отличие от Д118.4: там проверка не отличает новую блокировку от старых, здесь у блокировки не проверены её реквизиты</t>
+          <t>…понял, что тесты-шаги зависят друг от друга через общее состояние и порядок запуска. Засчитываем и замечание по симптому: шаг 2, запущенный отдельно, падает с NullPointerException. Отличие от Д113.2: там нет трейса, здесь шаги зависят друг от друга</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Д118.2</t>
+          <t>Д113.2</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>TK900118</t>
+          <t>TK900113</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>ArrestOnCurrentAccountTest.java:78</t>
+          <t>TK900113Test.java:34–40</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>getObject() вместо getRandomObject(10): все прогоны, в том числе параллельные, берут один и тот же первый договор и арестовывают его по очереди</t>
+          <t>Свой контекст создаётся без записи трейса, а методы BaseTest, которые трейс начинают и сохраняют, переопределены пустыми: у TK900113 нет трейса Playwright, по упавшему шагу не посмотреть, что было на странице</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>…понял, что параллельные или повторные прогоны будут брать один договор и мешать друг другу</t>
+          <t>…заметил, что у этого теста не пишется или не сохраняется трейс. Отличие от Д113.1: там шаги зависят друг от друга, здесь при падении нечем разобраться. Засчитываем и замечание по симптому: в build/traces нет файла TK900113</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Д118.3</t>
+          <t>Д113.3</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>TK900118</t>
+          <t>TK900113</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>ArrestOnCurrentAccountTest.java:100, ArrestOnCurrentAccountTest.java:110</t>
+          <t>TK900113Test.java:29</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Приватные методы с запросами без @Step: в Allure не видно, какие запросы выполнялись и что вернули, падение не привязано к шагу</t>
+          <t>Адрес песочницы зашит в тест вместо Config.baseUrl(): на стенде или на другом порту тест откроет не то приложение или не откроет ничего</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что запросы проверок не видны в отчёте</t>
+          <t>…указал на зашитый адрес. Засчитываем и замечание по симптому: при запуске на другом порту TK900113 падает с ERR_CONNECTION_REFUSED. Отличие от Д113.2: там нет трейса, здесь зашит адрес</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Д118.4</t>
+          <t>Д113.4</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>TK900118</t>
+          <t>TK900113</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ArrestOnCurrentAccountTest.java:102–105, ArrestOnCurrentAccountTest.java:58–59</t>
+          <t>TK900113Test.java:63–64</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>countHolds считает все блокировки договора, в том числе закрытые и старые. У выбранного договора уже есть закрытая блокировка, поэтому isPositive() пройдёт, даже если арест не создан</t>
+          <t>Шаг 2: не проверено, что появилась кнопка «Снять временную блокировку». Если кнопки нет, тест упадёт только на шаге 3, когда попробует её нажать, и падение шага 3 будет указывать не на ту причину</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка не отличает новую блокировку от старых или пройдёт без ареста. Засчитываем, если названо место запроса или проверки. Если участник написал только, что у проверки нет сообщения, — не засчитываем. Отличие от Д118.1: там не проверены вид, сумма и состояние. Отличие от Д118.5: там запрос не выполнится на PostgreSQL, здесь выполнится, но посчитает не то</t>
+          <t>…заметил непроверенный ожидаемый результат шага 2. Отличие от Д113.5: здесь проверки нет совсем, там она есть, но сверяет не то</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Д118.5</t>
+          <t>Д113.5</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>TK900118</t>
+          <t>TK900113</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>ArrestOnCurrentAccountTest.java:113, ArrestOnCurrentAccountTest.java:118</t>
+          <t>TK900113Test.java:72–73</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>NVL и SYSDATE есть только в Oracle, а тест идёт и на PostgreSQL-стенде: там запрос падает. Нужно COALESCE и CURRENT_DATE</t>
+          <t>Шаг 3: вместо «статус — «Активна»» проверяется, что статус не «Временно заблокирована». Сразу после подтверждения статус «Обработка…», поэтому проверка проходит мгновенно, ещё до ответа сервиса; если снять блокировку не удастся, тест всё равно зелёный</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>…указал, что запрос не выполнится на PostgreSQL. Засчитываем, если назван хотя бы один из двух операторов. Засчитываем и замечание по симптому: на PGRF1RT тест падает на строке 47 с ошибкой про SYSDATE. Отличие от Д118.4: там запрос работает везде, но считает лишние блокировки</t>
+          <t>…понял, что проверка «не равно» не сверяет статус с ожидаемым или проходит на промежуточном статусе. Засчитываем и замечание по симптому: шаг 3 идёт 0,04 секунды, хотя снятие блокировки занимает около секунды. Отличие от Д113.4: там не проверен шаг 2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Д119.1</t>
+          <t>Д114.1</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>TK900119</t>
+          <t>TK900114</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>CloseCurrentAccountTest.java:44, CloseCurrentAccountTest.java:96–103</t>
+          <t>TK900114Test.java:28–29</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Тест сам обнуляет остаток прямым UPDATE с фиксацией, в обход проводок: деньги клиента на общем стенде пропадают, остаток расходится с документами, другие тесты получают сломанные данные. Проверяется не тот сценарий. Нужно искать договор с нулевым остатком</t>
+          <t>Вкладка открывается через dispatchEvent("click"): событие отправляется элементу напрямую, без проверок обычного клика — видна ли вкладка, доступна ли, не перекрыта ли. Тест откроет вкладку, которую пользователь не видит или не может нажать, а настоящая причина, почему «клик не срабатывает», так и останется неизвестной. Заодно пропадает шаг Allure «Открыть вкладку» из CardPage</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>…указал на прямое изменение данных стенда в обход бизнес-логики или на то, что изменения не откатываются</t>
+          <t>…понял, что вкладка открывается в обход проверок Playwright и не так, как это делает пользователь, или предложил обычный клик через описание страницы</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Д119.2</t>
+          <t>Д114.2</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>TK900119</t>
+          <t>TK900114</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>CloseCurrentAccountTest.java:48–52</t>
+          <t>TK900114Test.java:30, TK900114Test.java:41–43</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>catch глотает ошибку ЦФТ при закрытии: тест идёт дальше, минуту ждёт состояние «Закрыт» и падает на нём, а причина отказа остаётся только в логе</t>
+          <t>isCardNumberMasked ловит PlaywrightException и возвращает false, а тест проверяет результат через assertTrue без сообщения. При падении в отчёте будет только «expected: &lt;true&gt; but was: &lt;false&gt;»: не узнать, не нашёлся элемент, истекло ожидание или текст другой. Нужна проверка assertThat(cardPage.requisite("cardNumber")).hasText(...): она сама ждёт и пишет фактический текст</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>…понял, что ошибка операции глотается и по падению не понять, почему договор не закрылся. Засчитываем и замечание по симптому: тест через 60 секунд падает на строке 55 «ожидалось состояние CLOSE, фактически WORK», если указана причина — проглоченная ошибка</t>
+          <t>…указал, что причина падения теряется: ошибка глотается или проверка без сообщения. Замечание засчитываем и у вызова, и у метода. Засчитываем и замечание, что маска проверяется самодельным методом, который читает текст один раз, вместо проверки Playwright, которая повторяет сверку до таймаута. Отличие от Д114.5: там проверка слабая, здесь при падении не понять, что сломалось</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Д119.3</t>
+          <t>Д114.3</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>TK900119</t>
+          <t>TK900114</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>CloseCurrentAccountTest.java:54–56</t>
+          <t>TK900114Test.java:31</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Ожидаемый результат «счёт договора закрыт» не проверяется: проверены только состояние и дата закрытия договора</t>
+          <t>page.getByText(holderName).first() ищет ФИО по всей странице и берёт первое совпадение — ФИО в шапке профиля, она стоит раньше реквизитов. Проверка пройдёт, даже если в реквизитах другой держатель или вкладка не открылась. Без first() Playwright упал бы с strict mode violation: first() спрятал эту ошибку, вместо того чтобы сузить поиск</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>…указал, что не проверено состояние счёта. Отличие от Д119.4: там проверка даты есть, но ничего не сравнивает, здесь проверки счёта нет совсем</t>
+          <t>…указал, что держатель ищется не в блоке реквизитов или что берётся ФИО из шапки. Отличие от Д114.5: там не сверяется номер карты, здесь — держатель. Отличие от Д114.4: там срок действия ищется по номеру элемента</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Д119.4</t>
+          <t>Д114.4</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>TK900119</t>
+          <t>TK900114</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>CloseCurrentAccountTest.java:56</t>
+          <t>TK900114Test.java:32</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Дата закрытия сравнивается сама с собой (deposit.getDateClose()), а не с текущим операционным днём: проверка проходит при любой дате</t>
+          <t>Срок действия ищется позиционным xpath «третий dd на странице». Локатор зависит от порядка полей и не привязан к реквизитам: на вкладке «Обзор» третий dd — тоже срок действия, поэтому проверка пройдёт, даже если вкладка «Реквизиты» не открылась. Нужно поле expiry внутри блока реквизитов</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>…понял, что ожидаемое значение берётся из проверяемого объекта и проверка ничего не проверяет. Отличие от Д119.3: там не проверен счёт, здесь проверка даты договора есть, но пустая</t>
+          <t>…указал на хрупкий локатор по номеру элемента или на то, что он не привязан к блоку реквизитов. Отличие от Д114.3: там держатель ищется по всей странице</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Д119.5</t>
+          <t>Д114.5</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>TK900119</t>
+          <t>TK900114</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>CloseCurrentAccountTest.java:70–72</t>
+          <t>TK900114Test.java:40</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Свой фрагмент вместо withoutActiveCard(): условие на правую таблицу LEFT JOIN стоит в WHERE. Договоры без карт отсекаются (NULL &lt;&gt; 'ACTIVE' не истинно), а договор с закрытой и действующей картой проходит по строке закрытой карты. Тест берёт договор с действующей картой, и ЦФТ его не закрывает</t>
+          <t>Маска проверяется только по началу «•••• »: последние 4 цифры с номером карты не сверяются, пройдёт и номер чужой карты</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>…понял хотя бы одно из последствий: договоры без карт отсекаются или договор с действующей картой проходит. Засчитываем и предложение вернуть готовый метод отбора без действующих карт или NOT EXISTS. Засчитываем и замечание по симптому: в логе «По договору есть действующие карты», если указана причина — условие на карты</t>
+          <t>…заметил, что последние 4 цифры не проверяются. Отличие от Д114.2: здесь проверка слишком слабая, там она теряет причину падения</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Д120.1</t>
+          <t>Д115.1</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>TK900120</t>
+          <t>TK900115</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>OpenAccountWithExpiredDocTest.java:51–53</t>
+          <t>TK900115Test.java:27</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Проверяется только, что ошибка не пустая: тест пройдёт при любом отказе, например «не указан продавец», а кейс требует текст «Срок действия документа, удостоверяющего личность, истёк»</t>
+          <t>Остаток проверяется по части текста «0,00»: пройдёт и для «10 000,00 ₽». Кейс требует ровно «0,00 ₽», от этого зависит, можно ли закрыть карту</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>…понял, что текст ошибки не сравнивается с ожидаемым. Отличие от Д120.2: там речь о проверке, что договор не создан</t>
+          <t>…понял, что проверка по части текста пропустит ненулевой остаток. Отличие от Д115.5: там не проверена запись в истории</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Д120.2</t>
+          <t>Д115.2</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>TK900120</t>
+          <t>TK900115</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>OpenAccountWithExpiredDocTest.java:57</t>
+          <t>TK900115Test.java:31–32</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>«Договор не создан» проверяется поиском договора в состоянии «Работает», а новый договор создаётся в состоянии «Ожидает подтверждения»: ошибочно созданный договор проверка не найдёт</t>
+          <t>Клик по пункту меню с setForce(true): Playwright не ждёт, пока пункт станет видимым, доступным и неподвижным. Обычный клик по недоступному пункту (у неактивной карты он помечен aria-disabled) упал бы с понятной причиной в журнале — «waiting for element to be visible, enabled and stable». Принудительный клик проходит молча, окно не открывается, и тест падает дальше, на проверке окна, без настоящей причины</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>…понял, что фильтр по состоянию «Работает» делает проверку бесполезной. Отличие от Д120.1: там не сверяется текст ошибки. Отличие от Д120.3: там проверка неудобна при падении, здесь она ищет не тот договор</t>
+          <t>…понял, что принудительный клик отключает проверки перед действием и прячет причину, если пункт недоступен</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Д120.3</t>
+          <t>Д115.3</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>TK900120</t>
+          <t>TK900115</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>OpenAccountWithExpiredDocTest.java:61</t>
+          <t>TK900115Test.java:39</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>assertThat(deposit == null).isTrue() вместо проверки объекта: при падении в отчёте только «expected true», без номера найденного договора</t>
+          <t>Код ответа проверяется через assertTrue(response.ok()) без сообщения: при падении в отчёте только «expected: &lt;true&gt; but was: &lt;false&gt;», какой код вернул сервис закрытия, не видно. Нужно assertEquals(200, response.status(), "Код ответа сервиса закрытия карты")</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>…указал, что по падению не понять, какой договор нашёлся, и предложил проверку отсутствия объекта. Отличие от Д120.2: там поиск не найдёт ошибочный договор, здесь проверка немая</t>
+          <t>…указал, что по падению не понять, какой код вернулся</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Д120.4</t>
+          <t>Д115.4</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>TK900120</t>
+          <t>TK900115</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>OpenAccountWithExpiredDocTest.java:74</t>
+          <t>TK900115Test.java:46</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Клиент зашит ID с RTEST вместо условия «ДУЛ истёк на дату»: на INTEST у клиентов другие ID и тест не находит данных; на любом стенде клиенту могут продлить паспорт</t>
+          <t>Перед шагом 4 страница обновляется, хотя в кейсе этого нет. Комментарий утверждает, что без обновления история не подтягивается: если так, это ошибка приложения, и тест должен её поймать, а не обойти. На деле история загружается при каждом открытии вкладки, обновление лишнее</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>…указал на зашитый ID клиента и предложил искать клиента по сроку ДУЛ. Засчитываем и замечание по симптому: на INTEST тест падает на строке 92 «Клиент ФЛ не найден», если причина — зашитый ID. Отличие от Д120.5: там пропущено условие на пользователя</t>
+          <t>…заметил, что обновления страницы нет в кейсе, или что тест подстраивается под возможную ошибку. Засчитываем и замечание, что комментарий неверен: история грузится при каждом открытии вкладки. Отличие от Д115.5: здесь лишнее действие перед проверкой истории, там сама проверка неполная</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Д120.5</t>
+          <t>Д115.5</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>TK900120</t>
+          <t>TK900115</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>OpenAccountWithExpiredDocTest.java:82–84</t>
+          <t>TK900115Test.java:48</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Операционист ищется без филиала клиента, хотя кейс требует операциониста филиала клиента: может попасться пользователь другого филиала с другим операционным днём или без доступа к клиенту. Тогда договор не откроется по другой причине, а проверка «ошибка не пустая» (Д120.1) примет это за ожидаемый отказ</t>
+          <t>Шаг 4: проверяется только, что таблица истории видна, а не что в ней есть запись «Закрытие карты». Таблица видна у любой карты</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что пользователь не привязан к филиалу клиента. Отличие от Д120.4: там зашит клиент, здесь у пользователя пропущено условие</t>
+          <t>…заметил, что запись «Закрытие карты» не проверяется. Отличие от Д115.4: там лишнее обновление страницы. Отличие от Д115.1: там неточно проверен остаток</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Д111.1</t>
+          <t>Д116.1</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>TK900111</t>
+          <t>TK900116</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>TK900111Test.java:13</t>
+          <t>OpenCurrentAccountTest.java:62–65</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>В @DisplayName номер чужого кейса TK-900115: в отчёте и в Test IT результат окажется под чужим номером, трейс тоже назван по TK-900115, а у TK-900111 результата не будет</t>
+          <t>Шаг 2: номер счёта договора не проверяется, хотя кейс требует, чтобы он начинался с 40817; проверены только состояния договора и счёта</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что номер кейса в названии теста не тот. Засчитываем и замечание по симптому: в build/traces два файла «TK-900115 …» и нет файла TK-900111</t>
+          <t>…заметил, что не проверен номер счёта (балансовый счёт 40817)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Д111.2</t>
+          <t>Д116.2</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>TK900111</t>
+          <t>TK900116</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>TK900111Test.java:20–22</t>
+          <t>OpenCurrentAccountTest.java:71</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1: статус «Активна» после открытия карты не проверяется</t>
+          <t>Филиал зашит: вместо филиалов, у которых операционный день совпадает с текущей датой, тест всегда идёт в Московский РФ. Комментарий «клиенты с FATCA только в этом филиале» описывает данные одного стенда, и даже там неверен: такие клиенты есть и в Тверском РФ. Если у филиала закроют день или на другом стенде клиентов там нет, тест не найдёт данных</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>…заметил непроверенный ожидаемый результат шага 1. Отличие от Д111.5: здесь проверки нет совсем, там она есть, но не может упасть</t>
+          <t>…указал, что филиал зашит и тест привязан к данным одного стенда, или что пропала проверка операционного дня филиала</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Д111.3</t>
+          <t>Д116.3</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>TK900111</t>
+          <t>TK900116</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>TK900111Test.java:26</t>
+          <t>OpenCurrentAccountTest.java:86</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>page.waitForTimeout(5000) — фиксированная пауза вместо ожидания по условию. Блокировка в песочнице идёт 2 секунды, остальные 3 секунды тест просто стоит, а на медленном стенде 5 секунд может не хватить</t>
+          <t>NOT IN по подзапросу, где бывают пустые C_CLIENT (производство ещё не сопоставлено с клиентом): при хотя бы одном пустом значении NOT IN не возвращает ни одной строки, клиент не находится никогда. Нужно NOT EXISTS с условием ep.C_CLIENT = cp.ID</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>…указал на паузу и предложил ждать статуса. Засчитываем и замечание по симптому: TK900111 идёт 7–8 секунд, хотя делает не больше других. Отличие от Д111.4: здесь лишняя пауза, там проверка статуса, которая без этой паузы не работает</t>
+          <t>…связал NOT IN с пустыми значениями в подзапросе и понял, что запрос вернёт пустой результат. Засчитываем и предложение заменить на NOT EXISTS или отсечь пустые значения. Засчитываем и замечание по симптому: тест падает на строке 101 «Клиент ФЛ не найден», если указана причина — условие про исполнительные производства. Отличие от Д116.4: там запрос находит лишних клиентов, здесь не находит никого</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Д111.4</t>
+          <t>Д116.4</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>TK900111</t>
+          <t>TK900116</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>TK900111Test.java:27</t>
+          <t>OpenCurrentAccountTest.java:87–92</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Статус читается через textContent() и сравнивается в assertEquals: значение берётся в момент вызова, без автоожидания. Проверка проходит только благодаря паузе в строке 26: без паузы тест падает с «expected: &lt;Заблокирована&gt; but was: &lt;Обработка…&gt;». Нужно assertThat(cardPage.status()).hasText("Заблокирована")</t>
+          <t>В условии FATCA OR без скобок: AND связывает сильнее, вторая ветка не привязана к клиенту, и при любой чужой действующей форме с датой окончания EXISTS истинно для всех клиентов. Тест берёт клиента без FATCA, открытие договора падает с ошибкой ЦФТ. Скобки, которые QueryBuilder ставит вокруг условия целиком, не помогают — ошибка внутри подзапроса</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>…понял, что эта проверка не ждёт статуса и держится на паузе. Отличие от Д111.3: там лишняя пауза, здесь проверка, которая без этой паузы не работает. Замечание «убрать паузу и проверять статус с ожиданием» засчитываем за оба дефекта, если названы обе строки</t>
+          <t>…указал на OR без скобок и понял, что фильтр по клиенту теряется или что найдутся клиенты без формы FATCA. Засчитываем и замечание по симптому: после исправления Д116.3 тест падает на строке 52 с ошибкой ЦФТ «У клиента нет действующей формы FATCA», если причина — условие на FATCA. Отличие от Д116.3: там не находится никто, здесь находятся лишние клиенты</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Д111.5</t>
+          <t>Д116.5</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>TK900111</t>
+          <t>TK900116</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>TK900111Test.java:30–33</t>
+          <t>OpenCurrentAccountTest.java:101</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Проверка видимости баннера в if не ждёт и смотрит на состояние в эту секунду: если баннера нет, проверка просто не выполняется, а если он есть, проверка внутри if подтверждает уже известное. Ожидаемый результат «отображается баннер» фактически не проверяется</t>
+          <t>После цикла проверяется только клиент. Если операциониста не нашлось, тест упадёт с NullPointerException в authorization(user), и непонятно, что не нашлись данные</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка баннера не может упасть. Засчитываем и формулировку, что условие не ждёт появления баннера. Отличие от Д111.2: там проверки статуса нет совсем, здесь проверка баннера есть, но не может упасть</t>
+          <t>…указал, что пользователь после поиска не проверяется и падение будет непонятным</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Д112.1</t>
+          <t>Д117.1</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>TK900112</t>
+          <t>TK900117</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>TK900112Test.java:15–17</t>
+          <t>CashDepositToCurrentAccountTest.java:77–79</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Личный долгоживущий JWT-токен (владелец ivanov_ii) в коде вместо токена из Config. Токен даёт доступ к API под чужой учёткой и попадёт в репозиторий. Протухание токена решается в Config — он и так берёт новый токен заранее</t>
+          <t>Комментарий говорит, что на стендах RF проводка идёт до 10 минут, а проверка ждёт состояние «Выполнена» со стандартным таймаутом 60 секунд: на стендах RF тест будет падать, хотя проводка просто идёт дольше</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>…указал на токен в коде</t>
+          <t>…заметил, что ожидание короче, чем нужно по комментарию, или что ожидание проводки слишком короткое для стендов RF</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Д112.2</t>
+          <t>Д117.2</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>TK900112</t>
+          <t>TK900117</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>TK900112Test.java:24–26</t>
+          <t>CashDepositToCurrentAccountTest.java:83</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1: вкладка «Лимиты» не открывается, значение по умолчанию 200 000 не проверяется</t>
+          <t>Остаток проверяется как «больше, чем был»: пройдёт при любом увеличении, а кейс требует ровно +1 500,00 ₽</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что не проверено значение по умолчанию. Отличие от Д112.4: там не проверено значение после обновления страницы, здесь — до изменения</t>
+          <t>…понял, что проверка не сверяет сумму увеличения. Замечание, что у проверки нет сообщения, засчитываем, только если сказано и то, что сумма не сверяется</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Д112.3</t>
+          <t>Д117.3</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>TK900112</t>
+          <t>TK900117</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>TK900112Test.java:31</t>
+          <t>CashDepositToCurrentAccountTest.java:101</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Значение поля после сохранения читается через page.querySelector(...): это ElementHandle в обход локаторов CardPage, без автоожидания и по CSS с именем поля. Значение берётся в момент вызова: если поле перерисуется позже, проверка прочитает старое значение, а если поле не найдётся, тест упадёт с NullPointerException. Нужно assertThat(cardPage.transferLimitInput()).hasValue("150 000")</t>
+          <t>Состояние «Работает» задано ID записи справочника RTEST. ID справочника генерируется на каждом стенде свой, одинаков только код: на INTEST тест не найдёт ни одного договора. Нужно withStatusEqualTo(ComStatusPrd.$WORK)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>…указал, что значение в поле проверяется без ожидания или в обход описания страницы. Отличие от Д112.5: там лишнее ожидание после обновления страницы, здесь чтение значения без ожидания на шаге 2</t>
+          <t>…указал, что ID справочника зависит от стенда, или предложил фильтр по коду состояния. Засчитываем и замечание по симптому: на INTEST тест падает на строке 124 «Договор не найден», если причина — ID состояния. Отличие от Д117.4: там зашит пользователь, здесь — запись справочника</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Д112.4</t>
+          <t>Д117.4</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>TK900112</t>
+          <t>TK900117</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>TK900112Test.java:33–35</t>
+          <t>CashDepositToCurrentAccountTest.java:115</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3: после обновления страницы вкладка «Лимиты» не открывается и значение 150 000 не проверяется — сохранился ли лимит, тест не знает</t>
+          <t>Кассир зашит логином kassir_mn с одного стенда и одного подразделения, а кейс требует кассира подразделения договора. На другом стенде или при смене сотрудника тест сломается</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что после обновления страницы ничего не проверено. Отличие от Д112.5: здесь нет проверки, там лишнее ожидание. Отличие от Д112.2: там не проверено значение до изменения</t>
+          <t>…указал на зашитый логин пользователя или предложил искать кассира по подразделению договора и роли. Отличие от Д117.3: там зашита запись справочника</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Д112.5</t>
+          <t>Д117.5</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>TK900112</t>
+          <t>TK900117</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>TK900112Test.java:35</t>
+          <t>CashDepositToCurrentAccountTest.java:133–136, CashDepositToCurrentAccountTest.java:60–61</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>waitForLoadState(NETWORKIDLE) — ожидание тишины в сети, документация Playwright не советует его в тестах. Тишина в сети не значит, что на странице нужные данные, а если страница постоянно что-то запрашивает в фоне, тишина не наступит и тест упадёт по таймауту. Нужно не ожидание, а проверка значения в поле: она ждёт сама</t>
+          <t>«Последняя» операция берётся без ORDER BY и без фильтра по сумме и дате: FETCH FIRST 1 ROWS ONLY возвращает произвольную строку. У договоров есть история операций, тест берёт старую проведённую операцию</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>…указал, что ожидание тишины в сети ненадёжно или не нужно, раз проверка с автоожиданием ждёт сама. Отличие от Д112.4: там нет проверки после обновления. Отличие от Д112.3: там значение читается без ожидания</t>
+          <t>…указал, что без сортировки порядок строк не определён, или что запрос не отличает созданную операцию от старых. Засчитываем, если названо место запроса или его вызова. Засчитываем и замечание по симптому: тест через 60 секунд падает на строках 63–65 — у операции состояние PERFORMED вместо ADD_CONTROL, если указана причина — берётся не та операция. Отличие от Д117.3: там договор не находится вовсе, здесь находится не та операция</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Д113.1</t>
+          <t>Д118.1</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>TK900113</t>
+          <t>TK900118</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>TK900113Test.java:16–17, TK900113Test.java:21–26, TK900113Test.java:47–48, TK900113Test.java:59–60, TK900113Test.java:67–68</t>
+          <t>ArrestOnCurrentAccountTest.java:58–59</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Шаги кейса — три отдельных теста с @Order, общими полями и одной страницей на класс. Шаги зависят друг от друга: шаг 2 или 3 отдельно не запустить, cardPage равен null; если упал шаг 1, шаги 2–3 падают с посторонними ошибками; в отчёте один кейс превращается в три результата. Нужен один тест, шаги — через Allure.step</t>
+          <t>Вид «Арест», сумма 5 000,00 ₽ и состояние «Действует» созданной блокировки не проверяются: из ожидаемых результатов проверен только доступный остаток</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>…понял, что тесты-шаги зависят друг от друга через общее состояние и порядок запуска. Засчитываем и замечание по симптому: шаг 2, запущенный отдельно, падает с NullPointerException. Отличие от Д113.2: там нет трейса, здесь шаги зависят друг от друга</t>
+          <t>…указал, что не проверены вид, сумма или состояние блокировки. Отличие от Д118.4: там проверка не отличает новую блокировку от старых, здесь у блокировки не проверены её реквизиты</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Д113.2</t>
+          <t>Д118.2</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>TK900113</t>
+          <t>TK900118</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>TK900113Test.java:28–32, TK900113Test.java:34–40</t>
+          <t>ArrestOnCurrentAccountTest.java:78</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Свой контекст создаётся без записи трейса, а методы BaseTest, которые трейс начинают и сохраняют, переопределены пустыми: у TK900113 нет трейса Playwright, по упавшему шагу не посмотреть, что было на странице</t>
+          <t>getObject() вместо getRandomObject(10): все прогоны, в том числе параллельные, берут один и тот же первый договор и арестовывают его по очереди</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что у этого теста не пишется или не сохраняется трейс. Отличие от Д113.1: там шаги зависят друг от друга, здесь при падении нечем разобраться. Засчитываем и замечание по симптому: в build/traces нет файла TK900113</t>
+          <t>…понял, что параллельные или повторные прогоны будут брать один договор и мешать друг другу</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Д113.3</t>
+          <t>Д118.3</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>TK900113</t>
+          <t>TK900118</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>TK900113Test.java:29</t>
+          <t>ArrestOnCurrentAccountTest.java:100, ArrestOnCurrentAccountTest.java:110</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Адрес песочницы зашит в тест вместо Config.baseUrl(): на стенде или на другом порту тест откроет не то приложение или не откроет ничего</t>
+          <t>Приватные методы с запросами без @Step: в Allure не видно, какие запросы выполнялись и что вернули, падение не привязано к шагу</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>…указал на зашитый адрес. Засчитываем и замечание по симптому: при запуске на другом порту TK900113 падает с ERR_CONNECTION_REFUSED. Отличие от Д113.2: там нет трейса, здесь зашит адрес</t>
+          <t>…заметил, что запросы проверок не видны в отчёте</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Д113.4</t>
+          <t>Д118.4</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>TK900113</t>
+          <t>TK900118</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>TK900113Test.java:63–64</t>
+          <t>ArrestOnCurrentAccountTest.java:102–105</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2: не проверено, что появилась кнопка «Снять временную блокировку». Если кнопки нет, тест упадёт только на шаге 3, когда попробует её нажать, и падение шага 3 будет указывать не на ту причину</t>
+          <t>countHolds считает все блокировки договора, в том числе закрытые и старые. У выбранного договора уже есть закрытая блокировка, поэтому isPositive() пройдёт, даже если арест не создан</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>…заметил непроверенный ожидаемый результат шага 2. Отличие от Д113.5: здесь проверки нет совсем, там она есть, но сверяет не то</t>
+          <t>…понял, что проверка не отличает новую блокировку от старых или пройдёт без ареста. Засчитываем и замечание у проверки в строках 58–59, если причина — подсчёт всех блокировок договора. Если участник написал только, что у проверки нет сообщения, — не засчитываем. Отличие от Д118.1: там не проверены вид, сумма и состояние. Отличие от Д118.5: там запрос не выполнится на PostgreSQL, здесь выполнится, но посчитает не то</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Д113.5</t>
+          <t>Д118.5</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>TK900113</t>
+          <t>TK900118</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>TK900113Test.java:72–73</t>
+          <t>ArrestOnCurrentAccountTest.java:113, ArrestOnCurrentAccountTest.java:118</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3: вместо «статус — «Активна»» проверяется, что статус не «Временно заблокирована». Сразу после подтверждения статус «Обработка…», поэтому проверка проходит мгновенно, ещё до ответа сервиса; если снять блокировку не удастся, тест всё равно зелёный</t>
+          <t>NVL и SYSDATE есть только в Oracle, а тест идёт и на PostgreSQL-стенде: там запрос падает. Нужно COALESCE и CURRENT_DATE</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка «не равно» не сверяет статус с ожидаемым или проходит на промежуточном статусе. Засчитываем и замечание по симптому: шаг 3 идёт 0,04 секунды, хотя снятие блокировки занимает около секунды. Отличие от Д113.4: там не проверен шаг 2</t>
+          <t>…указал, что запрос не выполнится на PostgreSQL. Засчитываем, если назван хотя бы один из двух операторов. Засчитываем и замечание по симптому: на PGRF1RT тест падает на строке 47 с ошибкой про SYSDATE. Отличие от Д118.4: там запрос работает везде, но считает лишние блокировки</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Д114.1</t>
+          <t>Д119.1</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>TK900114</t>
+          <t>TK900119</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>TK900114Test.java:28–29</t>
+          <t>CloseCurrentAccountTest.java:44, CloseCurrentAccountTest.java:96–103</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Вкладка открывается через dispatchEvent("click"): событие отправляется элементу напрямую, без проверок обычного клика — видна ли вкладка, доступна ли, не перекрыта ли. Тест откроет вкладку, которую пользователь не видит или не может нажать, а настоящая причина, почему «клик не срабатывает», так и останется неизвестной. Заодно пропадает шаг Allure «Открыть вкладку» из CardPage</t>
+          <t>Тест сам обнуляет остаток прямым UPDATE с фиксацией, в обход проводок: деньги клиента на общем стенде пропадают, остаток расходится с документами, другие тесты получают сломанные данные. Проверяется не тот сценарий. Нужно искать договор с нулевым остатком</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>…понял, что вкладка открывается в обход проверок Playwright и не так, как это делает пользователь, или предложил обычный клик через описание страницы</t>
+          <t>…указал на прямое изменение данных стенда в обход бизнес-логики или на то, что изменения не откатываются</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Д114.2</t>
+          <t>Д119.2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>TK900114</t>
+          <t>TK900119</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>TK900114Test.java:30, TK900114Test.java:41–43</t>
+          <t>CloseCurrentAccountTest.java:48–52</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>isCardNumberMasked ловит PlaywrightException и возвращает false, а тест проверяет результат через assertTrue без сообщения. При падении в отчёте будет только «expected: &lt;true&gt; but was: &lt;false&gt;»: не узнать, не нашёлся элемент, истекло ожидание или текст другой. Нужна проверка assertThat(cardPage.requisite("cardNumber")).hasText(...): она сама ждёт и пишет фактический текст</t>
+          <t>catch глотает ошибку ЦФТ при закрытии: тест идёт дальше, минуту ждёт состояние «Закрыт» и падает на нём, а причина отказа остаётся только в логе</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>…указал, что причина падения теряется: ошибка глотается или проверка без сообщения. Замечание засчитываем и у вызова, и у метода. Засчитываем и замечание, что маска проверяется самодельным методом, который читает текст один раз, вместо проверки Playwright, которая повторяет сверку до таймаута. Отличие от Д114.5: там проверка слабая, здесь при падении не понять, что сломалось</t>
+          <t>…понял, что ошибка операции глотается и по падению не понять, почему договор не закрылся. Засчитываем и замечание по симптому: тест через 60 секунд падает на строке 55 «ожидалось состояние CLOSE, фактически WORK», если указана причина — проглоченная ошибка</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Д114.3</t>
+          <t>Д119.3</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>TK900114</t>
+          <t>TK900119</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>TK900114Test.java:31</t>
+          <t>CloseCurrentAccountTest.java:54–55</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>page.getByText(holderName).first() ищет ФИО по всей странице и берёт первое совпадение — ФИО в шапке профиля, она стоит раньше реквизитов. Проверка пройдёт, даже если в реквизитах другой держатель или вкладка не открылась. Без first() Playwright упал бы с strict mode violation: first() спрятал эту ошибку, вместо того чтобы сузить поиск</t>
+          <t>Ожидаемый результат «счёт договора закрыт» не проверяется: проверены только состояние и дата закрытия договора</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>…указал, что держатель ищется не в блоке реквизитов или что берётся ФИО из шапки. Отличие от Д114.5: там не сверяется номер карты, здесь — держатель. Отличие от Д114.4: там срок действия ищется по номеру элемента</t>
+          <t>…указал, что не проверено состояние счёта. Отличие от Д119.4: там проверка даты есть, но ничего не сравнивает, здесь проверки счёта нет совсем</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Д114.4</t>
+          <t>Д119.4</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>TK900114</t>
+          <t>TK900119</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>TK900114Test.java:32</t>
+          <t>CloseCurrentAccountTest.java:56</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Срок действия ищется позиционным xpath «третий dd на странице». Локатор зависит от порядка полей и не привязан к реквизитам: на вкладке «Обзор» третий dd — тоже срок действия, поэтому проверка пройдёт, даже если вкладка «Реквизиты» не открылась. Нужно поле expiry внутри блока реквизитов</t>
+          <t>Дата закрытия сравнивается сама с собой (deposit.getDateClose()), а не с текущим операционным днём: проверка проходит при любой дате</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>…указал на хрупкий локатор по номеру элемента или на то, что он не привязан к блоку реквизитов. Отличие от Д114.3: там держатель ищется по всей странице</t>
+          <t>…понял, что ожидаемое значение берётся из проверяемого объекта и проверка ничего не проверяет. Отличие от Д119.3: там не проверен счёт, здесь проверка даты договора есть, но пустая</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Д114.5</t>
+          <t>Д119.5</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>TK900114</t>
+          <t>TK900119</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>TK900114Test.java:40</t>
+          <t>CloseCurrentAccountTest.java:70–72</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Маска проверяется только по началу «•••• »: последние 4 цифры с номером карты не сверяются, пройдёт и номер чужой карты</t>
+          <t>Свой фрагмент вместо withoutActiveCard(): условие на правую таблицу LEFT JOIN стоит в WHERE. Договоры без карт отсекаются (NULL &lt;&gt; 'ACTIVE' не истинно), а договор с закрытой и действующей картой проходит по строке закрытой карты. Тест берёт договор с действующей картой, и ЦФТ его не закрывает</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что последние 4 цифры не проверяются. Отличие от Д114.2: здесь проверка слишком слабая, там она теряет причину падения</t>
+          <t>…понял хотя бы одно из последствий: договоры без карт отсекаются или договор с действующей картой проходит. Засчитываем и предложение вернуть готовый метод отбора без действующих карт или NOT EXISTS. Засчитываем и замечание по симптому: в логе «По договору есть действующие карты», если указана причина — условие на карты</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Д115.1</t>
+          <t>Д120.1</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>TK900115</t>
+          <t>TK900120</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>TK900115Test.java:27</t>
+          <t>OpenAccountWithExpiredDocTest.java:51–53</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Остаток проверяется по части текста «0,00»: пройдёт и для «10 000,00 ₽». Кейс требует ровно «0,00 ₽», от этого зависит, можно ли закрыть карту</t>
+          <t>Проверяется только, что ошибка не пустая: тест пройдёт при любом отказе, например «не указан продавец», а кейс требует текст «Срок действия документа, удостоверяющего личность, истёк»</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка по части текста пропустит ненулевой остаток. Отличие от Д115.5: там не проверена запись в истории</t>
+          <t>…понял, что текст ошибки не сравнивается с ожидаемым. Отличие от Д120.2: там речь о проверке, что договор не создан</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Д115.2</t>
+          <t>Д120.2</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>TK900115</t>
+          <t>TK900120</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>TK900115Test.java:31–32</t>
+          <t>OpenAccountWithExpiredDocTest.java:57</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Клик по пункту меню с setForce(true): Playwright не ждёт, пока пункт станет видимым, доступным и неподвижным. Обычный клик по недоступному пункту (у неактивной карты он помечен aria-disabled) упал бы с понятной причиной в журнале — «waiting for element to be visible, enabled and stable». Принудительный клик проходит молча, окно не открывается, и тест падает дальше, на проверке окна, без настоящей причины</t>
+          <t>«Договор не создан» проверяется поиском договора в состоянии «Работает», а новый договор создаётся в состоянии «Ожидает подтверждения»: ошибочно созданный договор проверка не найдёт</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>…понял, что принудительный клик отключает проверки перед действием и прячет причину, если пункт недоступен</t>
+          <t>…понял, что фильтр по состоянию «Работает» делает проверку бесполезной. Отличие от Д120.1: там не сверяется текст ошибки. Отличие от Д120.3: там проверка неудобна при падении, здесь она ищет не тот договор</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Д115.3</t>
+          <t>Д120.3</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>TK900115</t>
+          <t>TK900120</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>TK900115Test.java:39</t>
+          <t>OpenAccountWithExpiredDocTest.java:61</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Код ответа проверяется через assertTrue(response.ok()) без сообщения: при падении в отчёте только «expected: &lt;true&gt; but was: &lt;false&gt;», какой код вернул сервис закрытия, не видно. Нужно assertEquals(200, response.status(), "Код ответа сервиса закрытия карты")</t>
+          <t>assertThat(deposit == null).isTrue() вместо проверки объекта: при падении в отчёте только «expected true», без номера найденного договора</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>…указал, что по падению не понять, какой код вернулся</t>
+          <t>…указал, что по падению не понять, какой договор нашёлся, или предложил проверку отсутствия объекта. Отличие от Д120.2: там поиск не найдёт ошибочный договор, здесь проверка немая</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Д115.4</t>
+          <t>Д120.4</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>TK900115</t>
+          <t>TK900120</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>TK900115Test.java:46</t>
+          <t>OpenAccountWithExpiredDocTest.java:74</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Перед шагом 4 страница обновляется, хотя в кейсе этого нет. Комментарий утверждает, что без обновления история не подтягивается: если так, это ошибка приложения, и тест должен её поймать, а не обойти. На деле история загружается при каждом открытии вкладки, обновление лишнее</t>
+          <t>Клиент зашит ID с RTEST вместо условия «ДУЛ истёк на дату»: на INTEST у клиентов другие ID и тест не находит данных; на любом стенде клиенту могут продлить паспорт</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что обновления страницы нет в кейсе, или что тест подстраивается под возможную ошибку. Засчитываем и замечание, что комментарий неверен: история грузится при каждом открытии вкладки. Отличие от Д115.5: здесь лишнее действие перед проверкой истории, там сама проверка неполная</t>
+          <t>…указал на зашитый ID клиента или предложил искать клиента по сроку ДУЛ. Засчитываем и замечание по симптому: на INTEST тест падает на строке 92 «Клиент ФЛ не найден», если причина — зашитый ID. Отличие от Д120.5: там пропущено условие на пользователя</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Д115.5</t>
+          <t>Д120.5</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>TK900115</t>
+          <t>TK900120</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>TK900115Test.java:48</t>
+          <t>OpenAccountWithExpiredDocTest.java:82–84</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4: проверяется только, что таблица истории видна, а не что в ней есть запись «Закрытие карты». Таблица видна у любой карты</t>
+          <t>Операционист ищется без филиала клиента, хотя кейс требует операциониста филиала клиента: может попасться пользователь другого филиала с другим операционным днём или без доступа к клиенту. Тогда договор не откроется по другой причине, а проверка «ошибка не пустая» (Д120.1) примет это за ожидаемый отказ</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что запись «Закрытие карты» не проверяется. Отличие от Д115.4: там лишнее обновление страницы. Отличие от Д115.1: там неточно проверен остаток</t>
+          <t>…заметил, что пользователь не привязан к филиалу клиента. Отличие от Д120.4: там зашит клиент, здесь у пользователя пропущено условие</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,12 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Ставим 1, если участник предлагает «исправить» это место. Если сам объяснил, почему код верен, — 0. Каждая ловушка −2 балла</t>
+          <t>Ставим 1, если участник считает это место ошибкой. Если сам объяснил, почему код верен, — 0. Каждая ловушка −2 балла</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>Попался (1/0)</t>
         </is>
       </c>
     </row>
@@ -3315,17 +3320,17 @@
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>CriteriaR2Deposit.java:116–118</t>
+          <t>BaseTest.java:23–25, BaseTest.java:32–36, BaseTest.java:43–49</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>LEFT JOIN … ON … AND h.C_STATE = 'ACTIVE' и WHERE h.ID IS NULL — правильный анти-join: остаются договоры, у которых нет ни одной действующей блокировки. Условие на состояние стоит в ON, поэтому LEFT JOIN не превращается во внутренний. В Д119.5 условие стоит в WHERE — там ошибка</t>
+          <t>Статические Playwright и Browser на класс, а BrowserContext и Page — свои у каждого теста. Так советует документация Playwright: запуск браузера дорогой, а cookies, хранилище и сессия живут в контексте, поэтому тесты изолированы. В TK900113 общий на класс ещё и контекст со страницей — там это дефект (Д113.1)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>«Условие на правую таблицу LEFT JOIN — ошибка, как в TK900119» или «LEFT JOIN надо заменить на NOT EXISTS»</t>
+          <t>«Браузер общий на все тесты — тесты делят состояние»</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3343,17 @@
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:93, CashDepositToCurrentAccountTest.java:102, CloseCurrentAccountTest.java:73, OpenAccountWithExpiredDocTest.java:75</t>
+          <t>TK900115Test.java:37–38</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Случайный выбор из первых десяти — принятый в проекте способ развести параллельные прогоны по разным данным. Параметры поиска и выбранный объект пишутся в лог и Allure, так что упавший прогон можно воспроизвести. Дефект — наоборот, всегда первый договор (Д118.2)</t>
+          <t>waitForResponse вокруг клика — ожидание по условию: тест ждёт ответ сервиса закрытия, а не фиксированное время</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>«Тест недетерминирован из-за случайных данных», «надо брать первую строку»</t>
+          <t>«Это тоже ожидание, как sleep»</t>
         </is>
       </c>
     </row>
@@ -3361,17 +3366,17 @@
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>BaseTest.java:23–25, BaseTest.java:32–36, BaseTest.java:43–49</t>
+          <t>TK900115Test.java:41</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Статические Playwright и Browser на класс, а BrowserContext и Page — свои у каждого теста. Так советует документация Playwright: запуск браузера дорогой, а cookies, хранилище и сессия живут в контексте, поэтому тесты изолированы. В TK900113 общий на класс ещё и контекст со страницей — там это дефект (Д113.1)</t>
+          <t>assertThat(dialog).isHidden() для окна, которое было открыто (строка 34), ждёт, пока оно закроется. Проверка не может пройти раньше, чем окно появилось</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>«Браузер общий на все тесты — тесты делят состояние»</t>
+          <t>«Проверка, что окна нет, пройдёт сразу и ничего не ловит»</t>
         </is>
       </c>
     </row>
@@ -3384,17 +3389,17 @@
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>TK900115Test.java:37–38</t>
+          <t>CriteriaR2Deposit.java:116–118</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>waitForResponse вокруг клика — ожидание по условию: тест ждёт ответ сервиса закрытия, а не фиксированное время</t>
+          <t>LEFT JOIN … ON … AND h.C_STATE = 'ACTIVE' и WHERE h.ID IS NULL — правильный анти-join: остаются договоры, у которых нет ни одной действующей блокировки. Условие на состояние стоит в ON, поэтому LEFT JOIN не превращается во внутренний. В Д119.5 условие стоит в WHERE — там ошибка</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>«Это тоже ожидание, как sleep»</t>
+          <t>«Условие на правую таблицу LEFT JOIN — ошибка, как в TK900119» или «LEFT JOIN надо заменить на NOT EXISTS»</t>
         </is>
       </c>
     </row>
@@ -3407,17 +3412,17 @@
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>TK900115Test.java:41</t>
+          <t>OpenCurrentAccountTest.java:93, CashDepositToCurrentAccountTest.java:102, CloseCurrentAccountTest.java:73, OpenAccountWithExpiredDocTest.java:75</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>assertThat(dialog).isHidden() для окна, которое было открыто (строка 34), ждёт, пока оно закроется. Проверка не может пройти раньше, чем окно появилось</t>
+          <t>Случайный выбор из первых десяти — принятый в проекте способ развести параллельные прогоны по разным данным. Параметры поиска и выбранный объект пишутся в лог и Allure, так что упавший прогон можно воспроизвести. Дефект — наоборот, всегда первый договор (Д118.2)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>«Проверка, что окна нет, пройдёт сразу и ничего не ловит»</t>
+          <t>«Тест недетерминирован из-за случайных данных», «надо брать первую строку»</t>
         </is>
       </c>
     </row>

--- a/review-tasks/1a-autotest-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1a-autotest-review/jury/scoring-sheet.xlsx
@@ -1862,17 +1862,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>TK900111Test.java:20–22</t>
+          <t>TK900111Test.java:23</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1: статус «Активна» после открытия карты не проверяется</t>
+          <t>Начальный статус проверяется как «не Закрыта» вместо точного «Активна». Заблокированная или временно заблокированная карта тоже пройдёт, хотя предусловие кейса не выполнено</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>…заметил непроверенный ожидаемый результат шага 1. Отличие от Д111.5: здесь проверки нет совсем, там она есть, но не может упасть</t>
+          <t>…указал, что отрицательная проверка допускает другой неактивный статус, или предложил проверить точное «Активна». Отличие от Д111.4: там ожидание статуса после блокировки; от Д111.5 — баннер</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>TK900111Test.java:26</t>
+          <t>TK900111Test.java:27</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>TK900111Test.java:27</t>
+          <t>TK900111Test.java:28</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Статус читается через textContent() и сравнивается в assertEquals: значение берётся в момент вызова, без автоожидания. Проверка проходит только благодаря паузе в строке 26: без паузы тест падает с «expected: &lt;Заблокирована&gt; but was: &lt;Обработка…&gt;». Нужно assertThat(cardPage.status()).hasText("Заблокирована")</t>
+          <t>Статус читается через textContent() и сравнивается в assertEquals: значение берётся в момент вызова, без автоожидания. Проверка проходит только благодаря паузе в строке 27: без паузы тест падает с «expected: &lt;Заблокирована&gt; but was: &lt;Обработка…&gt;». Нужно assertThat(cardPage.status()).hasText("Заблокирована")</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>TK900111Test.java:30–33</t>
+          <t>TK900111Test.java:31–34</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка баннера не может упасть. Засчитываем и формулировку, что условие не ждёт появления баннера. Отличие от Д111.2: там проверки статуса нет совсем, здесь проверка баннера есть, но не может упасть</t>
+          <t>…понял, что проверка баннера не может упасть. Засчитываем и формулировку, что условие не ждёт появления баннера. Отличие от Д111.2: там отрицательная проверка начального статуса допускает неактивную карту, здесь проверка баннера не может упасть</t>
         </is>
       </c>
     </row>
@@ -1997,17 +1997,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>TK900112Test.java:24–26</t>
+          <t>TK900112Test.java:28</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1: вкладка «Лимиты» не открывается, значение по умолчанию 200 000 не проверяется</t>
+          <t>Первоначальный лимит проверяется только на непустоту поля, а кейс требует 200 000. Любой другой непустой лимит пройдёт</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что не проверено значение по умолчанию. Отличие от Д112.4: там не проверено значение после обновления страницы, здесь — до изменения</t>
+          <t>…указал, что непустое поле не подтверждает лимит 200 000. Отличие от Д112.4: там проверка после обновления страницы</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>TK900112Test.java:31</t>
+          <t>TK900112Test.java:33</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>TK900112Test.java:33–34</t>
+          <t>TK900112Test.java:37</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3: после обновления страницы вкладка «Лимиты» не открывается и значение 150 000 не проверяется — сохранился ли лимит, тест не знает</t>
+          <t>После обновления страницы лимит не проверяется. Комментарий «Лимит уже проверили до обновления страницы — повторно проверять незачем» подменяет проверку сохранения прежней проверкой поля: исчезнувшее после reload значение тест не заметит</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что после обновления страницы ничего не проверено. Отличие от Д112.5: здесь нет проверки, там лишнее ожидание. Отличие от Д112.2: там не проверено значение до изменения</t>
+          <t>…указал, что после обновления нужно заново открыть «Лимиты» и проверить 150 000, либо что проверка до обновления не доказывает сохранение. Отличие от Д112.5: там ненадёжное ожидание сети</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>TK900112Test.java:35</t>
+          <t>TK900112Test.java:38</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>TK900113Test.java:16–17, TK900113Test.java:21–26, TK900113Test.java:47–48, TK900113Test.java:59–60, TK900113Test.java:67–68</t>
+          <t>TK900113Test.java:22–27</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>TK900113Test.java:34–40</t>
+          <t>TK900113Test.java:35–41</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>TK900113Test.java:29</t>
+          <t>TK900113Test.java:30</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2186,17 +2186,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>TK900113Test.java:63–64</t>
+          <t>TK900113Test.java:66–67</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2: не проверено, что появилась кнопка «Снять временную блокировку». Если кнопки нет, тест упадёт только на шаге 3, когда попробует её нажать, и падение шага 3 будет указывать не на ту причину</t>
+          <t>Кнопка «Снять временную блокировку» проверяется только на enabled, хотя кейс требует, чтобы она отображалась. Локатор getByText находит и скрытую кнопку; isEnabled не требует её видимости. Скрытая, но enabled кнопка пройдёт проверку</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>…заметил непроверенный ожидаемый результат шага 2. Отличие от Д113.5: здесь проверки нет совсем, там она есть, но сверяет не то</t>
+          <t>…указал, что доступность кнопки не подтверждает её отображение, или предложил проверку видимости. Отличие от Д113.5: там неверная проверка статуса после снятия блокировки</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>TK900113Test.java:72–73</t>
+          <t>TK900113Test.java:75–76</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка «не равно» не сверяет статус с ожидаемым или проходит на промежуточном статусе. Засчитываем и замечание по симптому: шаг 3 идёт 0,04 секунды, хотя снятие блокировки занимает около секунды. Отличие от Д113.4: там не проверен шаг 2</t>
+          <t>…понял, что проверка «не равно» не сверяет статус с ожидаемым или проходит на промежуточном статусе. Засчитываем и замечание по симптому: шаг 3 идёт 0,04 секунды, хотя снятие блокировки занимает около секунды. Отличие от Д113.4: там доступность кнопки проверяется вместо видимости</t>
         </is>
       </c>
     </row>
@@ -2267,17 +2267,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>TK900114Test.java:30, TK900114Test.java:41–43</t>
+          <t>TK900114Test.java:41–42</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>isCardNumberMasked ловит PlaywrightException и возвращает false, а тест проверяет результат через assertTrue без сообщения. При падении в отчёте будет только «expected: &lt;true&gt; but was: &lt;false&gt;»: не узнать, не нашёлся элемент, истекло ожидание или текст другой. Нужна проверка assertThat(cardPage.requisite("cardNumber")).hasText(...): она сама ждёт и пишет фактический текст</t>
+          <t>В catch исходный PlaywrightException заменяется на false. Ошибка поиска или ожидания элемента превращается в сообщение о неверной маске, теряются исходная причина и журнал Playwright. У assertTrue есть описание, но оно не восстанавливает проглоченное исключение</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>…указал, что причина падения теряется: ошибка глотается или проверка без сообщения. Замечание засчитываем и у вызова, и у метода. Засчитываем и замечание, что маска проверяется самодельным методом, который читает текст один раз, вместо проверки Playwright, которая повторяет сверку до таймаута. Отличие от Д114.5: там проверка слабая, здесь при падении не понять, что сломалось</t>
+          <t>…указал на потерю причины PlaywrightException из-за return false, либо предложил не глотать исключение или сохранить его причиной падения. Отсутствие автоожидания, обход page object и отсутствие сообщения у проверки отдельно за этот дефект не засчитываем. Отличие от Д114.5: там проверяется только начало маски</t>
         </is>
       </c>
     </row>
@@ -2510,17 +2510,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:62–65</t>
+          <t>OpenCurrentAccountTest.java:67</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2: номер счёта договора не проверяется, хотя кейс требует, чтобы он начинался с 40817; проверены только состояния договора и счёта</t>
+          <t>Номер счёта проверяется только по префиксу 408, хотя кейс требует 40817. Например, номер на балансовом счёте 40820 тоже пройдёт</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что не проверен номер счёта (балансовый счёт 40817)</t>
+          <t>…указал, что префикс проверяется не полностью, либо предложил 40817 или hasAccountStartWith(BalanceAccount.$40817)</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:71</t>
+          <t>OpenCurrentAccountTest.java:73</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:86</t>
+          <t>OpenCurrentAccountTest.java:88</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:87–92</t>
+          <t>OpenCurrentAccountTest.java:89–94</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2618,17 +2618,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:101</t>
+          <t>OpenCurrentAccountTest.java:104</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>После цикла проверяется только клиент. Если операциониста не нашлось, тест упадёт с NullPointerException в authorization(user), и непонятно, что не нашлись данные</t>
+          <t>Assertions.assertThat(user).as("Операционист найден") создаёт объект проверки и описание, но не содержит утверждения isNotNull: null не уронит эту строку. Если пользователь не найден, тест дойдёт до authorization(user) и упадёт с посторонней ошибкой</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>…указал, что пользователь после поиска не проверяется и падение будет непонятным</t>
+          <t>…заметил незавершённую проверку, отсутствие isNotNull или предложил AssertionsUtil.assertThat(user).objectExist()</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>CashDepositToCurrentAccountTest.java:133–136, CashDepositToCurrentAccountTest.java:60–61</t>
+          <t>CashDepositToCurrentAccountTest.java:133–136</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -2780,17 +2780,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>ArrestOnCurrentAccountTest.java:58–59</t>
+          <t>ArrestOnCurrentAccountTest.java:60</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Вид «Арест», сумма 5 000,00 ₽ и состояние «Действует» созданной блокировки не проверяются: из ожидаемых результатов проверен только доступный остаток</t>
+          <t>Вид найденной блокировки допускает ARREST или BLOCK, хотя кейс требует только «Арест». Обычная блокировка на ту же сумму и в том же состоянии пройдёт. Сумма 5 000,00, состояние ACTIVE и дата проверяются условиями getHoldKind; реквизиты не объединены в один пропуск</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>…указал, что не проверены вид, сумма или состояние блокировки. Отличие от Д118.4: там проверка не отличает новую блокировку от старых, здесь у блокировки не проверены её реквизиты</t>
+          <t>…указал, что BLOCK не должен удовлетворять проверке ареста, или предложил сравнивать только с ARREST. Отличие от Д118.4: там количество блокировок считается без фильтров</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ArrestOnCurrentAccountTest.java:78</t>
+          <t>ArrestOnCurrentAccountTest.java:82</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>ArrestOnCurrentAccountTest.java:100, ArrestOnCurrentAccountTest.java:110</t>
+          <t>ArrestOnCurrentAccountTest.java:104</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Приватные методы с запросами без @Step: в Allure не видно, какие запросы выполнялись и что вернули, падение не привязано к шагу</t>
+          <t>У countHolds нет @Step: выполнение проверочного запроса и его результат не видны отдельным шагом Allure. У getHoldKind и getAvailableBalance аннотации есть; дефект относится только к одному методу</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что запросы проверок не видны в отчёте</t>
+          <t>…указал на отсутствие шага отчёта у countHolds или непрозрачность этого SQL-запроса в Allure</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>ArrestOnCurrentAccountTest.java:102–105</t>
+          <t>ArrestOnCurrentAccountTest.java:106–109</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка не отличает новую блокировку от старых или пройдёт без ареста. Засчитываем и замечание у проверки в строках 58–59, если причина — подсчёт всех блокировок договора. Если участник написал только, что у проверки нет сообщения, — не засчитываем. Отличие от Д118.1: там не проверены вид, сумма и состояние. Отличие от Д118.5: там запрос не выполнится на PostgreSQL, здесь выполнится, но посчитает не то</t>
+          <t>…понял, что проверка не отличает новую блокировку от старых или пройдёт без ареста. Засчитываем и замечание у проверки в строках 62–63, если причина — подсчёт всех блокировок договора. Если участник написал только, что у проверки нет сообщения, — не засчитываем. Отличие от Д118.1: там допускается BLOCK вместо ARREST; сумма и состояние проверены в getHoldKind. Отличие от Д118.5: там запрос не выполнится на PostgreSQL, здесь выполнится, но посчитает не то</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>ArrestOnCurrentAccountTest.java:113, ArrestOnCurrentAccountTest.java:118</t>
+          <t>ArrestOnCurrentAccountTest.java:140</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>NVL и SYSDATE есть только в Oracle, а тест идёт и на PostgreSQL-стенде: там запрос падает. Нужно COALESCE и CURRENT_DATE</t>
+          <t>В запросе используется Oracle SYSDATE, а кейс выполняется и на PostgreSQL: там выражение не выполнится. Нужен CURRENT_DATE. COALESCE в этом же запросе корректен для обеих СУБД</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>…указал, что запрос не выполнится на PostgreSQL. Засчитываем, если назван хотя бы один из двух операторов. Засчитываем и замечание по симптому: на PGRF1RT тест падает на строке 47 с ошибкой про SYSDATE. Отличие от Д118.4: там запрос работает везде, но считает лишние блокировки</t>
+          <t>…указал, что SYSDATE несовместим с PostgreSQL, или предложил CURRENT_DATE. Засчитываем и падение на чтении доступного остатка с этой причиной. Отличие от Д118.4: там запрос выполнится, но посчитает лишние блокировки</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>CloseCurrentAccountTest.java:44, CloseCurrentAccountTest.java:96–103</t>
+          <t>CloseCurrentAccountTest.java:103–107</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>CloseCurrentAccountTest.java:48–52</t>
+          <t>CloseCurrentAccountTest.java:49–53</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>CloseCurrentAccountTest.java:54–55</t>
+          <t>CloseCurrentAccountTest.java:60</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Ожидаемый результат «счёт договора закрыт» не проверяется: проверены только состояние и дата закрытия договора</t>
+          <t>Счёт договора проверяется как «не OPEN», а не точным состоянием CLOSE. Любое другое состояние тоже удовлетворит проверке, хотя кейс требует закрытый счёт</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>…указал, что не проверено состояние счёта. Отличие от Д119.4: там проверка даты есть, но ничего не сравнивает, здесь проверки счёта нет совсем</t>
+          <t>…указал, что отрицательная проверка не доказывает закрытие счёта, или предложил точное состояние CLOSE. Отличие от Д119.4: там дата договора сравнивается сама с собой</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>CloseCurrentAccountTest.java:56</t>
+          <t>CloseCurrentAccountTest.java:57</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>CloseCurrentAccountTest.java:70–72</t>
+          <t>CloseCurrentAccountTest.java:74–76</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>OpenCurrentAccountTest.java:93, CashDepositToCurrentAccountTest.java:102, CloseCurrentAccountTest.java:73, OpenAccountWithExpiredDocTest.java:75</t>
+          <t>OpenCurrentAccountTest.java:95, CashDepositToCurrentAccountTest.java:102, CloseCurrentAccountTest.java:77, OpenAccountWithExpiredDocTest.java:75</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
